--- a/Data/Zone Spawn Sheet.xlsx
+++ b/Data/Zone Spawn Sheet.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="235">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -60,7 +60,7 @@
     <t xml:space="preserve">Social</t>
   </si>
   <si>
-    <t xml:space="preserve">a spiderling</t>
+    <t xml:space="preserve">spiderling</t>
   </si>
   <si>
     <t xml:space="preserve">A Spiderling Swarmer</t>
@@ -75,7 +75,7 @@
     <t xml:space="preserve">Insect</t>
   </si>
   <si>
-    <t xml:space="preserve">Web, (snaring attack)</t>
+    <t xml:space="preserve">necrotic_grasp</t>
   </si>
   <si>
     <t xml:space="preserve">a rat</t>
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Animal</t>
   </si>
   <si>
-    <t xml:space="preserve">a bat</t>
+    <t xml:space="preserve">bat</t>
   </si>
   <si>
     <t xml:space="preserve">A Dusk Bat</t>
@@ -102,10 +102,10 @@
     <t xml:space="preserve">Small winged creatures that emerge at dusk. Non-aggressive unless starving (heat wave events). More of an atmospheric element than real threat. Swarm mechanic if cornered.</t>
   </si>
   <si>
-    <t xml:space="preserve">Life Tap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a skeleton</t>
+    <t xml:space="preserve">life_siphon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skeleton</t>
   </si>
   <si>
     <t xml:space="preserve">A Fallen Scout Skeleton</t>
@@ -117,7 +117,7 @@
     <t xml:space="preserve">Humanoid</t>
   </si>
   <si>
-    <t xml:space="preserve">a goblin</t>
+    <t xml:space="preserve">goblin</t>
   </si>
   <si>
     <t xml:space="preserve">A Desert Goblin </t>
@@ -129,13 +129,16 @@
     <t xml:space="preserve">The common desert goblin—tribal warriors of medium build. Wear crude leather armor decorated with bones and tribal markings. Wield scimitars, daggers, or clubs. Territorial and aggressive but fight with basic tactics. Moderate threat for solo players.</t>
   </si>
   <si>
+    <t xml:space="preserve">goblin_scout</t>
+  </si>
+  <si>
     <t xml:space="preserve">A Desert Goblin Scout</t>
   </si>
   <si>
     <t xml:space="preserve">Smaller, quicker goblins that serve as lookouts for their tribes. Lean and wiry, wearing minimal armor. Armed with spears and throwing weapons. Flee when outnumbered but will alert nearby goblins. Less loot but faster experience for kiting practice.</t>
   </si>
   <si>
-    <t xml:space="preserve">a spider</t>
+    <t xml:space="preserve">spider</t>
   </si>
   <si>
     <t xml:space="preserve">A Giant Desert Spider</t>
@@ -147,10 +150,10 @@
     <t xml:space="preserve">Hairy arachnids with long, articulate legs adapted for sand traversal. Build webs between dunes to trap prey. Moderately aggressive, territorial around their dens.</t>
   </si>
   <si>
-    <t xml:space="preserve">Poison Bite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a bandit</t>
+    <t xml:space="preserve">crippling_poison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bandit</t>
   </si>
   <si>
     <t xml:space="preserve">A Sand Brigand</t>
@@ -159,7 +162,7 @@
     <t xml:space="preserve">Desperate outlaws and mercenaries operating on zone edges. Wear tattered armor, wield crude weapons. Work in small packs (2-3). Flee if losing badly. Can drop faction tokens.</t>
   </si>
   <si>
-    <t xml:space="preserve">a snake</t>
+    <t xml:space="preserve">snake</t>
   </si>
   <si>
     <t xml:space="preserve">A Sand Viper</t>
@@ -171,7 +174,7 @@
     <t xml:space="preserve">Reptile</t>
   </si>
   <si>
-    <t xml:space="preserve">a slime</t>
+    <t xml:space="preserve">slime</t>
   </si>
   <si>
     <t xml:space="preserve">An Acidic Slime</t>
@@ -186,7 +189,7 @@
     <t xml:space="preserve">Acid Attack</t>
   </si>
   <si>
-    <t xml:space="preserve">a dune scarab</t>
+    <t xml:space="preserve">dune_scarab</t>
   </si>
   <si>
     <t xml:space="preserve">A Dune Scarab</t>
@@ -198,7 +201,7 @@
     <t xml:space="preserve">Armored insects the size of a human torso, with iridescent shells that crack under sustained blows. Slow but powerful bite. Iconic to the desert, territorial creatures.</t>
   </si>
   <si>
-    <t xml:space="preserve">a ghost</t>
+    <t xml:space="preserve">ghost</t>
   </si>
   <si>
     <t xml:space="preserve">A Tormented Spirit</t>
@@ -210,6 +213,9 @@
     <t xml:space="preserve">Undead</t>
   </si>
   <si>
+    <t xml:space="preserve">goblin_warrior</t>
+  </si>
+  <si>
     <t xml:space="preserve">A Desert Goblin Warrior</t>
   </si>
   <si>
@@ -219,6 +225,18 @@
     <t xml:space="preserve">Larger, battle-hardened goblins that lead hunting parties and defend goblin camps. Muscular build, scarred faces, wearing reinforced armor. Wield heavier weapons (battleaxes, mauls). Coordinated and tactical—will flank or use terrain advantage. Significant threat, often found in groups guarding important areas.</t>
   </si>
   <si>
+    <t xml:space="preserve">mummy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Reanimated Sand Mummy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A risen mummy that guards the mausoleum area, attacking all who dare enter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plague_strike</t>
+  </si>
+  <si>
     <t xml:space="preserve">Old Name</t>
   </si>
   <si>
@@ -247,9 +265,6 @@
   </si>
   <si>
     <t xml:space="preserve">Fast Attack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spider</t>
   </si>
   <si>
     <t xml:space="preserve">A Plateau Spider</t>
@@ -1030,11 +1045,11 @@
     <tabColor rgb="FF3465A4"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27.96"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="66.64"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.53"/>
@@ -1175,16 +1190,16 @@
     </row>
     <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>30</v>
@@ -1192,36 +1207,36 @@
     </row>
     <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>30</v>
@@ -1229,56 +1244,56 @@
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>16</v>
@@ -1286,36 +1301,56 @@
     </row>
     <row r="13" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1349,10 +1384,10 @@
   <sheetData>
     <row r="1" s="7" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>2</v>
@@ -1388,16 +1423,16 @@
     <row r="2" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="1"/>
@@ -1409,22 +1444,22 @@
     </row>
     <row r="3" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -1435,22 +1470,22 @@
     </row>
     <row r="4" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -1461,22 +1496,22 @@
     </row>
     <row r="5" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -1487,22 +1522,22 @@
     </row>
     <row r="6" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -1513,22 +1548,22 @@
     </row>
     <row r="7" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -1539,22 +1574,22 @@
     </row>
     <row r="8" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1565,16 +1600,16 @@
     </row>
     <row r="9" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>30</v>
@@ -1590,16 +1625,16 @@
     <row r="10" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1"/>
       <c r="B10" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="1"/>
@@ -1611,22 +1646,22 @@
     </row>
     <row r="11" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -1637,22 +1672,22 @@
     </row>
     <row r="12" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1664,13 +1699,13 @@
     <row r="13" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="4"/>
@@ -1683,22 +1718,22 @@
     </row>
     <row r="14" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -1709,22 +1744,22 @@
     </row>
     <row r="15" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -1735,22 +1770,22 @@
     </row>
     <row r="16" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1762,16 +1797,16 @@
     <row r="17" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1"/>
       <c r="B17" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="1"/>
@@ -1784,19 +1819,19 @@
     <row r="18" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -1807,22 +1842,22 @@
     </row>
     <row r="19" customFormat="false" ht="141" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -1834,19 +1869,19 @@
     <row r="20" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -1943,10 +1978,10 @@
   <sheetData>
     <row r="1" s="3" customFormat="true" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>2</v>
@@ -1981,447 +2016,447 @@
     </row>
     <row r="2" customFormat="false" ht="115.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="102.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
